--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_los_lagos.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:47</t>
+    <t xml:space="preserve">2026-09-09 20:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_los_lagos.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:09</t>
+    <t xml:space="preserve">2026-09-18 17:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_los_lagos.xlsx
@@ -30,96 +30,96 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Palena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pablo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puyehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Varas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Negro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Juan de la Costa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Castro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualaihué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cochamó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frutillar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalcahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maullín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queilén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quellón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Muermos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llanquihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futaleufú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chonchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quemchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Octay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinchao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purranque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calbuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osorno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Montt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puqueldón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curaco de Vélez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chaitén</t>
   </si>
   <si>
-    <t xml:space="preserve">Curaco de Vélez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puqueldón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puerto Montt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Osorno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calbuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purranque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinchao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puerto Octay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quemchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chonchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Futaleufú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fresia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Llanquihue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Muermos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quellón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queilén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maullín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dalcahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frutillar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cochamó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ancud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualaihué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Castro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Juan de la Costa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Negro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puerto Varas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puyehue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pablo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palena</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:05</t>
+    <t xml:space="preserve">2026-09-27 21:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -549,13 +549,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4909</v>
+        <v>2537</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5050</v>
+        <v>1822</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>97.21</v>
+        <v>139.24</v>
       </c>
     </row>
     <row r="3">
@@ -563,13 +563,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4051</v>
+        <v>12921</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4104</v>
+        <v>10548</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>98.71</v>
+        <v>122.5</v>
       </c>
     </row>
     <row r="4">
@@ -577,13 +577,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4194</v>
+        <v>14091</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4195</v>
+        <v>11809</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>99.98</v>
+        <v>119.32</v>
       </c>
     </row>
     <row r="5">
@@ -591,13 +591,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>275938</v>
+        <v>57859</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>275473</v>
+        <v>50010</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>100.17</v>
+        <v>115.69</v>
       </c>
     </row>
     <row r="6">
@@ -605,13 +605,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>177166</v>
+        <v>16342</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>174998</v>
+        <v>14183</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>101.24</v>
+        <v>115.22</v>
       </c>
     </row>
     <row r="7">
@@ -619,13 +619,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>38139</v>
+        <v>8634</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>37221</v>
+        <v>7536</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>102.47</v>
+        <v>114.57</v>
       </c>
     </row>
     <row r="8">
@@ -633,13 +633,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>21595</v>
+        <v>54197</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>21028</v>
+        <v>48219</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>102.7</v>
+        <v>112.4</v>
       </c>
     </row>
     <row r="9">
@@ -647,13 +647,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>8468</v>
+        <v>10719</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>8241</v>
+        <v>9562</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>102.75</v>
+        <v>112.1</v>
       </c>
     </row>
     <row r="10">
@@ -661,13 +661,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9481</v>
+        <v>47455</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>9123</v>
+        <v>42507</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>103.92</v>
+        <v>111.64</v>
       </c>
     </row>
     <row r="11">
@@ -675,13 +675,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>9179</v>
+        <v>4391</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>8770</v>
+        <v>3976</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>104.66</v>
+        <v>110.44</v>
       </c>
     </row>
     <row r="12">
@@ -689,13 +689,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>16924</v>
+        <v>22602</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>16155</v>
+        <v>20535</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>104.76</v>
+        <v>110.07</v>
       </c>
     </row>
     <row r="13">
@@ -703,13 +703,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>3014</v>
+        <v>16681</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2862</v>
+        <v>15275</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>105.31</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="14">
@@ -717,13 +717,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>13306</v>
+        <v>16170</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>12616</v>
+        <v>14816</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>105.47</v>
+        <v>109.14</v>
       </c>
     </row>
     <row r="15">
@@ -731,13 +731,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>19836</v>
+        <v>5967</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>18755</v>
+        <v>5545</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>105.76</v>
+        <v>107.61</v>
       </c>
     </row>
     <row r="16">
@@ -745,13 +745,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>18888</v>
+        <v>31556</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>17831</v>
+        <v>29745</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>105.93</v>
+        <v>106.09</v>
       </c>
     </row>
     <row r="17">
@@ -759,13 +759,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>31556</v>
+        <v>18888</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>29745</v>
+        <v>17831</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>106.09</v>
+        <v>105.93</v>
       </c>
     </row>
     <row r="18">
@@ -773,13 +773,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>5967</v>
+        <v>19836</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>5545</v>
+        <v>18755</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>107.61</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="19">
@@ -787,13 +787,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>16170</v>
+        <v>13306</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>14816</v>
+        <v>12616</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>109.14</v>
+        <v>105.47</v>
       </c>
     </row>
     <row r="20">
@@ -801,13 +801,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>16681</v>
+        <v>3014</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>15275</v>
+        <v>2862</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>109.2</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="21">
@@ -815,13 +815,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>22602</v>
+        <v>16924</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>20535</v>
+        <v>16155</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>110.07</v>
+        <v>104.76</v>
       </c>
     </row>
     <row r="22">
@@ -829,13 +829,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>4391</v>
+        <v>9179</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>3976</v>
+        <v>8770</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>110.44</v>
+        <v>104.66</v>
       </c>
     </row>
     <row r="23">
@@ -843,13 +843,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>47455</v>
+        <v>9481</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>42507</v>
+        <v>9123</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>111.64</v>
+        <v>103.92</v>
       </c>
     </row>
     <row r="24">
@@ -857,13 +857,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>10719</v>
+        <v>8468</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>9562</v>
+        <v>8241</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>112.1</v>
+        <v>102.75</v>
       </c>
     </row>
     <row r="25">
@@ -871,13 +871,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>54197</v>
+        <v>21595</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>48219</v>
+        <v>21028</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>112.4</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="26">
@@ -885,13 +885,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>8634</v>
+        <v>38139</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>7536</v>
+        <v>37221</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>114.57</v>
+        <v>102.47</v>
       </c>
     </row>
     <row r="27">
@@ -899,13 +899,13 @@
         <v>29</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>16342</v>
+        <v>177166</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>14183</v>
+        <v>174998</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>115.22</v>
+        <v>101.24</v>
       </c>
     </row>
     <row r="28">
@@ -913,13 +913,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>57859</v>
+        <v>275938</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>50010</v>
+        <v>275473</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>115.69</v>
+        <v>100.17</v>
       </c>
     </row>
     <row r="29">
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>14091</v>
+        <v>4194</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>11809</v>
+        <v>4195</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>119.32</v>
+        <v>99.98</v>
       </c>
     </row>
     <row r="30">
@@ -941,13 +941,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>12921</v>
+        <v>4051</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>10548</v>
+        <v>4104</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>122.5</v>
+        <v>98.71</v>
       </c>
     </row>
     <row r="31">
@@ -955,13 +955,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>2537</v>
+        <v>4909</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1822</v>
+        <v>5050</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>139.24</v>
+        <v>97.21</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_los_lagos.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:51</t>
+    <t xml:space="preserve">2026-10-05 05:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
